--- a/input/ES/EUROMODpolicySchedule.xlsx
+++ b/input/ES/EUROMODpolicySchedule.xlsx
@@ -8,9 +8,133 @@
   <sheets>
     <sheet name="ES" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="40">
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Policy_Start_Year</t>
+  </si>
+  <si>
+    <t>Policy_System_Year</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>es_2018_std.txt</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>es_2008_std.txt</t>
+  </si>
+  <si>
+    <t>es_2011_std.txt</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>es_2010_std.txt</t>
+  </si>
+  <si>
+    <t>es_2009_std.txt</t>
+  </si>
+  <si>
+    <t>es_2019_std.txt</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>es_2012_std.txt</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>es_2024_std.txt</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>es_2025_std.txt</t>
+  </si>
+  <si>
+    <t>es_2013_std.txt</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>es_2006_std.txt</t>
+  </si>
+  <si>
+    <t>es_2016_std.txt</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>es_2020_std.txt</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>es_2021_std.txt</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>es_2017_std.txt</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>es_2007_std.txt</t>
+  </si>
+  <si>
+    <t>es_2023_std.txt</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>es_2005_std.txt</t>
+  </si>
+  <si>
+    <t>es_2015_std.txt</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>es_2014_std.txt</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>es_2022_std.txt</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,286 +548,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="1" width="17.85546875" customWidth="1" min="1" max="1"/>
-    <col collapsed="1" width="9.140625" customWidth="1" min="2" max="1025"/>
+    <col min="1" max="1" customWidth="true" width="17.85546875" collapsed="true"/>
+    <col min="2" max="1025" customWidth="true" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Policy_Start_Year</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Policy_System_Year</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>es_2018_std.txt</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>es_2011_std.txt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>es_2019_std.txt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>es_2012_std.txt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>es_2024_std.txt</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>es_2013_std.txt</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>es_2016_std.txt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>es_2020_std.txt</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>es_2021_std.txt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>es_2017_std.txt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>es_2023_std.txt</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>es_2015_std.txt</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>es_2014_std.txt</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>es_2022_std.txt</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
